--- a/data/access_paragraph_hate_speech_with_offenses.xlsx
+++ b/data/access_paragraph_hate_speech_with_offenses.xlsx
@@ -4787,7 +4787,7 @@
     <t>0,U,U,U,0,0,0,0</t>
   </si>
   <si>
-    <t>0,U,(1b;U),(1b,U),(6a;6b),0,0</t>
+    <t>0,U,(1b;U),(1b;U),(6a;6b),0,0,0</t>
   </si>
   <si>
     <t>0,0,0,6c,0,0,0,0</t>

--- a/data/access_paragraph_hate_speech_with_offenses.xlsx
+++ b/data/access_paragraph_hate_speech_with_offenses.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7304" uniqueCount="2866">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7304" uniqueCount="2865">
   <si>
     <t>ID</t>
   </si>
@@ -43,7 +43,7 @@
     <t xml:space="preserve">Ovaj Momirović je jedan od žešćih imbecila koji su bili u vlasti. Vređa inteligenciju! Mene sramota što sam Srbin kad slušam ovog, ne znam kako da ga nazovem!! On zajebava ovaj narod i treba da ga uništava kad je parizer brend!! Novak Đoković kad dođe da se nominuje onda ću da glasam jer ovo su ljudski odron! </t>
   </si>
   <si>
-    <t>twitter</t>
+    <t>X / Twitter</t>
   </si>
   <si>
     <t>U,U,0,(1b;U),U</t>
@@ -989,7 +989,7 @@
     <t>Biološka istraživanja se sprovode decenijama širom sveta. Ipak, rezultati jasno pokazuju da su određene rase evolutivno zaostale. Njihov niži IQ ih sprečava da doprinesu bilo čemu korisnom.  Oni su prosto genetski otpad civilizacije.</t>
   </si>
   <si>
-    <t>Gemini</t>
+    <t>LLM</t>
   </si>
   <si>
     <t>0,1a,1a,1a</t>
@@ -1343,7 +1343,7 @@
     <t>Vrlo je jednostavno, Jel se od nas ocekuje da zivotom branimo zenu i dete u slucaju bilo kakve opasnosti? Jel se od nas ocekuje da idemo u rat i ostavimo kosti negde kao branioci ili agresori. jel se ocekuje da budemo kavaljeri i cuvamo dom/zenu/otadzbinu od bilo kakve pretnje? ako je odgovor da, uzmite prezime i budite formalno deo kuce koju gradimo i cuvamo.</t>
   </si>
   <si>
-    <t>ispovesti</t>
+    <t>Reddit</t>
   </si>
   <si>
     <t>Zašto je onda u ratu najviše zločina silovanja kad su muškarci tako dobri zaštitnici? Ma daj, molim te. Ostavila sam svoje prezime i dodala njegovo jer smo mi nova obitelj od moje krvi i njegove.</t>
@@ -2084,7 +2084,7 @@
     <t>ta kineska savršena medicina uzgredno je pobila više ljudi i životinja nego pol pot. ako te zabadanje iglica u telo i jedenje čarobne supe od nosorogovih rogova, majmunskog mozga i slonove kljove ne izleči - onda neće ništa? taj mit o kineskoj medecini je posledica ljudske osobine da mitologizuje drevne civilizacije, drevna vremena i drevne ljude. kao, oni su kao znali nešto više, kao čovek je izgnan iz raja i luta dan danas i ostale priče za maštovitu decu. ali treba odrasti, kad tad.</t>
   </si>
   <si>
-    <t>portali</t>
+    <t>Meta</t>
   </si>
   <si>
     <t>Ispiranje mozga na centrifugu..,sex &amp; city sa primesama rijalitija. Evropa nema alternativu, gej je okej. Samo napred u reforme.</t>
@@ -2702,7 +2702,7 @@
     <t>Mene sramota što sam Srbin kad slušam ovog, ne znam kako da ga nazovem!! On zajebava ovaj narod i treba da ga uništava kad je parizer brend!! Novak Đoković kad dođe da se nominuje onda ću da glasam jer ovo su ljudski odron!</t>
   </si>
   <si>
-    <t>youtube</t>
+    <t>Youtube</t>
   </si>
   <si>
     <t>0,U,0</t>
@@ -2840,7 +2840,7 @@
     <t>@zoran  Poku veze nema sa Smailagicem.  Odavno je vec starter u svojoj ekipi. Redovno je medju boljim u plus minus kategoriji. Sut je sredio u odnosu na proslu sezonu. I uz sve to igra u timu americkih talentovanih klinaca divljaka koji bi pre bacali cigle sa trideset metara nego mu dodali loptu. Ko je gledao jednu partiju OKC zna o cemu pricam. Oni ko da svaku igraju tako kao da im je poslednja pred draft.  Ako realno gledamo Jokic, Bogdan, Poku, to su nam trenutno tri najjaca igraca. Vasa bi tesko bio starter u NBA, pa cak i u nekim Raketsima, a on nam je sledeci najbolji posle njih. Vasa je jako dobar, ali za NBA je prosecan, zapravo nije ni na nivou Dragica. Pustite me bajki o evropskoj kosarci. Kad tako neki krenu samo im uperim prstom na Mirotica koji je bio vec izduvan prosecnjak kada je otisao iz NBA, a u Evropi je kao takav harao. Jokic, Bogdan, Poku tim redom, bolje nemamo trenutno.</t>
   </si>
   <si>
-    <t>news</t>
+    <t>News</t>
   </si>
   <si>
     <t>0,0,0,0,U,0,0,0,0,0,0,U,0</t>
@@ -8463,9 +8463,6 @@
   </si>
   <si>
     <t>dobro, bre. pa, nije umro. došlo je vreme da uživa u životu, a ne da se seljaka od terena do bolnice i nazad.</t>
-  </si>
-  <si>
-    <t>LLM</t>
   </si>
   <si>
     <t>0,U,0,0,0,7</t>
@@ -9049,7 +9046,7 @@
   <cols>
     <col customWidth="1" min="1" max="1" width="6.43"/>
     <col customWidth="1" min="2" max="2" width="114.86"/>
-    <col customWidth="1" min="3" max="3" width="16.71"/>
+    <col customWidth="1" min="3" max="3" width="14.86"/>
     <col customWidth="1" min="4" max="5" width="61.14"/>
     <col customWidth="1" min="6" max="7" width="62.71"/>
   </cols>
@@ -41841,7 +41838,7 @@
   <sheetData>
     <row r="1">
       <c r="E1" s="3" t="s">
-        <v>2791</v>
+        <v>299</v>
       </c>
     </row>
     <row r="2">
@@ -41906,7 +41903,7 @@
     </row>
     <row r="14">
       <c r="E14" s="3" t="s">
-        <v>2792</v>
+        <v>2791</v>
       </c>
     </row>
     <row r="15">
@@ -41926,7 +41923,7 @@
     </row>
     <row r="18">
       <c r="E18" s="3" t="s">
-        <v>2793</v>
+        <v>2792</v>
       </c>
     </row>
     <row r="19">
@@ -41941,7 +41938,7 @@
     </row>
     <row r="21">
       <c r="E21" s="3" t="s">
-        <v>2794</v>
+        <v>2793</v>
       </c>
     </row>
     <row r="22">
@@ -42584,7 +42581,7 @@
     </row>
     <row r="182">
       <c r="E182" s="3" t="s">
-        <v>2795</v>
+        <v>2794</v>
       </c>
     </row>
     <row r="183">
@@ -42614,7 +42611,7 @@
     </row>
     <row r="188">
       <c r="E188" s="3" t="s">
-        <v>2796</v>
+        <v>2795</v>
       </c>
     </row>
     <row r="189">
@@ -42674,7 +42671,7 @@
     </row>
     <row r="200">
       <c r="E200" s="3" t="s">
-        <v>2797</v>
+        <v>2796</v>
       </c>
     </row>
     <row r="201">
@@ -42684,7 +42681,7 @@
     </row>
     <row r="202">
       <c r="E202" s="3" t="s">
-        <v>2798</v>
+        <v>2797</v>
       </c>
     </row>
     <row r="203">
@@ -42719,7 +42716,7 @@
     </row>
     <row r="209">
       <c r="E209" s="3" t="s">
-        <v>2799</v>
+        <v>2798</v>
       </c>
     </row>
     <row r="210">
@@ -42809,7 +42806,7 @@
     </row>
     <row r="227">
       <c r="E227" s="3" t="s">
-        <v>2800</v>
+        <v>2799</v>
       </c>
     </row>
     <row r="228">
@@ -42864,7 +42861,7 @@
     </row>
     <row r="238">
       <c r="E238" s="3" t="s">
-        <v>2801</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="239">
@@ -42874,7 +42871,7 @@
     </row>
     <row r="240">
       <c r="E240" s="3" t="s">
-        <v>2802</v>
+        <v>2801</v>
       </c>
     </row>
     <row r="241">
@@ -42909,7 +42906,7 @@
     </row>
     <row r="247">
       <c r="E247" s="3" t="s">
-        <v>2803</v>
+        <v>2802</v>
       </c>
     </row>
     <row r="248">
@@ -42929,7 +42926,7 @@
     </row>
     <row r="251">
       <c r="E251" s="3" t="s">
-        <v>2804</v>
+        <v>2803</v>
       </c>
     </row>
     <row r="252">
@@ -42964,17 +42961,17 @@
     </row>
     <row r="258">
       <c r="E258" s="3" t="s">
-        <v>2805</v>
+        <v>2804</v>
       </c>
     </row>
     <row r="259">
       <c r="E259" s="3" t="s">
-        <v>2806</v>
+        <v>2805</v>
       </c>
     </row>
     <row r="260">
       <c r="E260" s="3" t="s">
-        <v>2807</v>
+        <v>2806</v>
       </c>
     </row>
     <row r="261">
@@ -42994,7 +42991,7 @@
     </row>
     <row r="264">
       <c r="E264" s="3" t="s">
-        <v>2808</v>
+        <v>2807</v>
       </c>
     </row>
     <row r="265">
@@ -43014,7 +43011,7 @@
     </row>
     <row r="268">
       <c r="E268" s="3" t="s">
-        <v>2809</v>
+        <v>2808</v>
       </c>
     </row>
     <row r="269">
@@ -43024,17 +43021,17 @@
     </row>
     <row r="270">
       <c r="E270" s="3" t="s">
-        <v>2810</v>
+        <v>2809</v>
       </c>
     </row>
     <row r="271">
       <c r="E271" s="3" t="s">
-        <v>2811</v>
+        <v>2810</v>
       </c>
     </row>
     <row r="272">
       <c r="E272" s="3" t="s">
-        <v>2812</v>
+        <v>2811</v>
       </c>
     </row>
     <row r="273">
@@ -43049,7 +43046,7 @@
     </row>
     <row r="275">
       <c r="E275" s="3" t="s">
-        <v>2813</v>
+        <v>2812</v>
       </c>
     </row>
     <row r="276">
@@ -43064,17 +43061,17 @@
     </row>
     <row r="278">
       <c r="E278" s="3" t="s">
-        <v>2809</v>
+        <v>2808</v>
       </c>
     </row>
     <row r="279">
       <c r="E279" s="3" t="s">
-        <v>2814</v>
+        <v>2813</v>
       </c>
     </row>
     <row r="280">
       <c r="E280" s="3" t="s">
-        <v>2815</v>
+        <v>2814</v>
       </c>
     </row>
     <row r="281">
@@ -43099,7 +43096,7 @@
     </row>
     <row r="285">
       <c r="E285" s="3" t="s">
-        <v>2816</v>
+        <v>2815</v>
       </c>
     </row>
     <row r="286">
@@ -43134,7 +43131,7 @@
     </row>
     <row r="292">
       <c r="E292" s="3" t="s">
-        <v>2817</v>
+        <v>2816</v>
       </c>
     </row>
     <row r="293">
@@ -43149,7 +43146,7 @@
     </row>
     <row r="295">
       <c r="E295" s="3" t="s">
-        <v>2818</v>
+        <v>2817</v>
       </c>
     </row>
     <row r="296">
@@ -43184,7 +43181,7 @@
     </row>
     <row r="302">
       <c r="E302" s="3" t="s">
-        <v>2819</v>
+        <v>2818</v>
       </c>
     </row>
     <row r="303">
@@ -43199,7 +43196,7 @@
     </row>
     <row r="305">
       <c r="E305" s="3" t="s">
-        <v>2820</v>
+        <v>2819</v>
       </c>
     </row>
     <row r="306">
@@ -43209,7 +43206,7 @@
     </row>
     <row r="307">
       <c r="E307" s="3" t="s">
-        <v>2821</v>
+        <v>2820</v>
       </c>
     </row>
     <row r="308">
@@ -43234,12 +43231,12 @@
     </row>
     <row r="312">
       <c r="E312" s="3" t="s">
-        <v>2822</v>
+        <v>2821</v>
       </c>
     </row>
     <row r="313">
       <c r="E313" s="3" t="s">
-        <v>2823</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="314">
@@ -43249,7 +43246,7 @@
     </row>
     <row r="315">
       <c r="E315" s="3" t="s">
-        <v>2824</v>
+        <v>2823</v>
       </c>
     </row>
     <row r="316">
@@ -43274,7 +43271,7 @@
     </row>
     <row r="320">
       <c r="E320" s="3" t="s">
-        <v>2825</v>
+        <v>2824</v>
       </c>
     </row>
     <row r="321">
@@ -43309,7 +43306,7 @@
     </row>
     <row r="327">
       <c r="E327" s="3" t="s">
-        <v>2826</v>
+        <v>2825</v>
       </c>
     </row>
     <row r="328">
@@ -43334,7 +43331,7 @@
     </row>
     <row r="332">
       <c r="E332" s="3" t="s">
-        <v>2827</v>
+        <v>2826</v>
       </c>
     </row>
     <row r="333">
@@ -43354,7 +43351,7 @@
     </row>
     <row r="336">
       <c r="E336" s="3" t="s">
-        <v>2828</v>
+        <v>2827</v>
       </c>
     </row>
     <row r="337">
@@ -43369,32 +43366,32 @@
     </row>
     <row r="339">
       <c r="E339" s="3" t="s">
-        <v>2829</v>
+        <v>2828</v>
       </c>
     </row>
     <row r="340">
       <c r="E340" s="3" t="s">
-        <v>2830</v>
+        <v>2829</v>
       </c>
     </row>
     <row r="341">
       <c r="E341" s="3" t="s">
-        <v>2831</v>
+        <v>2830</v>
       </c>
     </row>
     <row r="342">
       <c r="E342" s="3" t="s">
-        <v>2832</v>
+        <v>2831</v>
       </c>
     </row>
     <row r="343">
       <c r="E343" s="3" t="s">
-        <v>2830</v>
+        <v>2829</v>
       </c>
     </row>
     <row r="344">
       <c r="E344" s="3" t="s">
-        <v>2833</v>
+        <v>2832</v>
       </c>
     </row>
     <row r="345">
@@ -43404,7 +43401,7 @@
     </row>
     <row r="346">
       <c r="E346" s="3" t="s">
-        <v>2834</v>
+        <v>2833</v>
       </c>
     </row>
     <row r="347">
@@ -43414,12 +43411,12 @@
     </row>
     <row r="348">
       <c r="E348" s="3" t="s">
-        <v>2835</v>
+        <v>2834</v>
       </c>
     </row>
     <row r="349">
       <c r="E349" s="3" t="s">
-        <v>2836</v>
+        <v>2835</v>
       </c>
     </row>
     <row r="350">
@@ -43429,17 +43426,17 @@
     </row>
     <row r="351">
       <c r="E351" s="3" t="s">
-        <v>2837</v>
+        <v>2836</v>
       </c>
     </row>
     <row r="352">
       <c r="E352" s="3" t="s">
-        <v>2838</v>
+        <v>2837</v>
       </c>
     </row>
     <row r="353">
       <c r="E353" s="3" t="s">
-        <v>2839</v>
+        <v>2838</v>
       </c>
     </row>
     <row r="354">
@@ -43479,7 +43476,7 @@
     </row>
     <row r="361">
       <c r="E361" s="3" t="s">
-        <v>2840</v>
+        <v>2839</v>
       </c>
     </row>
     <row r="362">
@@ -43509,7 +43506,7 @@
     </row>
     <row r="367">
       <c r="E367" s="3" t="s">
-        <v>2841</v>
+        <v>2840</v>
       </c>
     </row>
     <row r="368">
@@ -43529,7 +43526,7 @@
     </row>
     <row r="371">
       <c r="E371" s="3" t="s">
-        <v>2842</v>
+        <v>2841</v>
       </c>
     </row>
     <row r="372">
@@ -43564,12 +43561,12 @@
     </row>
     <row r="378">
       <c r="E378" s="3" t="s">
-        <v>2809</v>
+        <v>2808</v>
       </c>
     </row>
     <row r="379">
       <c r="E379" s="3" t="s">
-        <v>2840</v>
+        <v>2839</v>
       </c>
     </row>
     <row r="380">
@@ -43594,12 +43591,12 @@
     </row>
     <row r="384">
       <c r="E384" s="3" t="s">
-        <v>2843</v>
+        <v>2842</v>
       </c>
     </row>
     <row r="385">
       <c r="E385" s="3" t="s">
-        <v>2844</v>
+        <v>2843</v>
       </c>
     </row>
     <row r="386">
@@ -43624,12 +43621,12 @@
     </row>
     <row r="390">
       <c r="E390" s="3" t="s">
-        <v>2820</v>
+        <v>2819</v>
       </c>
     </row>
     <row r="391">
       <c r="E391" s="3" t="s">
-        <v>2845</v>
+        <v>2844</v>
       </c>
     </row>
     <row r="392">
@@ -43639,7 +43636,7 @@
     </row>
     <row r="393">
       <c r="E393" s="3" t="s">
-        <v>2820</v>
+        <v>2819</v>
       </c>
     </row>
     <row r="394">
@@ -43649,7 +43646,7 @@
     </row>
     <row r="395">
       <c r="E395" s="3" t="s">
-        <v>2846</v>
+        <v>2845</v>
       </c>
     </row>
     <row r="396">
@@ -43674,7 +43671,7 @@
     </row>
     <row r="400">
       <c r="E400" s="3" t="s">
-        <v>2847</v>
+        <v>2846</v>
       </c>
     </row>
     <row r="401">
@@ -43704,7 +43701,7 @@
     </row>
     <row r="406">
       <c r="E406" s="3" t="s">
-        <v>2848</v>
+        <v>2847</v>
       </c>
     </row>
     <row r="407">
@@ -43714,7 +43711,7 @@
     </row>
     <row r="408">
       <c r="E408" s="3" t="s">
-        <v>2849</v>
+        <v>2848</v>
       </c>
     </row>
     <row r="409">
@@ -43734,17 +43731,17 @@
     </row>
     <row r="412">
       <c r="E412" s="3" t="s">
-        <v>2850</v>
+        <v>2849</v>
       </c>
     </row>
     <row r="413">
       <c r="E413" s="3" t="s">
-        <v>2851</v>
+        <v>2850</v>
       </c>
     </row>
     <row r="414">
       <c r="E414" s="3" t="s">
-        <v>2852</v>
+        <v>2851</v>
       </c>
     </row>
     <row r="415">
@@ -43779,7 +43776,7 @@
     </row>
     <row r="421">
       <c r="E421" s="3" t="s">
-        <v>2853</v>
+        <v>2852</v>
       </c>
     </row>
     <row r="422">
@@ -43794,7 +43791,7 @@
     </row>
     <row r="424">
       <c r="E424" s="3" t="s">
-        <v>2854</v>
+        <v>2853</v>
       </c>
     </row>
     <row r="425">
@@ -43819,7 +43816,7 @@
     </row>
     <row r="429">
       <c r="E429" s="3" t="s">
-        <v>2855</v>
+        <v>2854</v>
       </c>
     </row>
     <row r="430">
@@ -43844,7 +43841,7 @@
     </row>
     <row r="434">
       <c r="E434" s="3" t="s">
-        <v>2856</v>
+        <v>2855</v>
       </c>
     </row>
     <row r="435">
@@ -43874,7 +43871,7 @@
     </row>
     <row r="440">
       <c r="E440" s="3" t="s">
-        <v>2857</v>
+        <v>2856</v>
       </c>
     </row>
     <row r="441">
@@ -43899,7 +43896,7 @@
     </row>
     <row r="445">
       <c r="E445" s="3" t="s">
-        <v>2809</v>
+        <v>2808</v>
       </c>
     </row>
     <row r="446">
@@ -43909,7 +43906,7 @@
     </row>
     <row r="447">
       <c r="E447" s="3" t="s">
-        <v>2858</v>
+        <v>2857</v>
       </c>
     </row>
     <row r="448">
@@ -43929,7 +43926,7 @@
     </row>
     <row r="451">
       <c r="E451" s="3" t="s">
-        <v>2859</v>
+        <v>2858</v>
       </c>
     </row>
     <row r="452">
@@ -43969,7 +43966,7 @@
     </row>
     <row r="459">
       <c r="E459" s="3" t="s">
-        <v>2860</v>
+        <v>2859</v>
       </c>
     </row>
     <row r="460">
@@ -43979,7 +43976,7 @@
     </row>
     <row r="461">
       <c r="E461" s="3" t="s">
-        <v>2809</v>
+        <v>2808</v>
       </c>
     </row>
     <row r="462">
@@ -43989,7 +43986,7 @@
     </row>
     <row r="463">
       <c r="E463" s="3" t="s">
-        <v>2809</v>
+        <v>2808</v>
       </c>
     </row>
     <row r="464">
@@ -44029,7 +44026,7 @@
     </row>
     <row r="471">
       <c r="E471" s="3" t="s">
-        <v>2861</v>
+        <v>2860</v>
       </c>
     </row>
     <row r="472">
@@ -44044,12 +44041,12 @@
     </row>
     <row r="474">
       <c r="E474" s="3" t="s">
-        <v>2809</v>
+        <v>2808</v>
       </c>
     </row>
     <row r="475">
       <c r="E475" s="3" t="s">
-        <v>2862</v>
+        <v>2861</v>
       </c>
     </row>
     <row r="476">
@@ -44069,7 +44066,7 @@
     </row>
     <row r="479">
       <c r="E479" s="3" t="s">
-        <v>2863</v>
+        <v>2862</v>
       </c>
     </row>
     <row r="480">
@@ -44089,7 +44086,7 @@
     </row>
     <row r="483">
       <c r="E483" s="3" t="s">
-        <v>2864</v>
+        <v>2863</v>
       </c>
     </row>
     <row r="484">
@@ -44099,7 +44096,7 @@
     </row>
     <row r="485">
       <c r="E485" s="3" t="s">
-        <v>2865</v>
+        <v>2864</v>
       </c>
     </row>
     <row r="486">
